--- a/WAF_Termine.xlsx
+++ b/WAF_Termine.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hochschulefresenius1-my.sharepoint.com/personal/caroline_zygar-hoffmann_charlotte-fresenius-uni_de/Documents/Lehre/WAF/WAF_Folien/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="275" documentId="13_ncr:1_{E1CA4565-1B9E-46AE-A3C7-26CD2293107D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC562142-82E0-4602-B420-BB8ACED740B4}"/>
+  <xr:revisionPtr revIDLastSave="377" documentId="13_ncr:1_{E1CA4565-1B9E-46AE-A3C7-26CD2293107D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26A8834A-2727-4622-B106-08AB628E727F}"/>
   <bookViews>
-    <workbookView xWindow="4635" yWindow="4635" windowWidth="28800" windowHeight="15435" xr2:uid="{2F7FBD6D-06A1-CD4E-B3C2-12F6DAD39F9F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{2F7FBD6D-06A1-CD4E-B3C2-12F6DAD39F9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
   <si>
     <t>Einheit</t>
   </si>
@@ -74,12 +74,6 @@
     <t>Daten sammeln</t>
   </si>
   <si>
-    <t>Operationalisierung &amp; formr</t>
-  </si>
-  <si>
-    <t>Operationalisierung &amp; Implementierung &amp; Testdurchlauf</t>
-  </si>
-  <si>
     <t>Analyseplan</t>
   </si>
   <si>
@@ -113,61 +107,124 @@
     <t>Analyseplan (am Beispiel Interventionsthema)</t>
   </si>
   <si>
-    <t>Gruppenfindung, Open Lab Book in GoogleDoc, Themenauswahl</t>
-  </si>
-  <si>
-    <t>Bis zum 26.04.: Abgabe Gruppenname &amp; Thema! ---- Feedback durch Caro, ist das Thema OK?</t>
-  </si>
-  <si>
     <t>Deadlines</t>
   </si>
   <si>
     <t>Supervision</t>
   </si>
   <si>
-    <t>Bis zum 24.05.: Finalisierung Präregistrierung</t>
-  </si>
-  <si>
     <t>Caro Feedback 4-5 Gruppen eigenes Thema; Nensy Feedback 4-5 Gruppen Interventionsthema</t>
   </si>
   <si>
-    <t>entfällt wegen Feiertag</t>
-  </si>
-  <si>
     <t xml:space="preserve">Poweranalyse &amp; OSF-Projekt &amp; Präregistrierung finalisieren </t>
   </si>
   <si>
     <t>Präregistrierung im Forschungsprozess &amp; Vorstellung Themenwahl</t>
   </si>
   <si>
-    <t>Literaturrecherche, Entwicklung Forschungsfrage</t>
-  </si>
-  <si>
-    <t>Ordnerstruktur, Hypothesen, Studiendesign, erste Analysegedanken</t>
-  </si>
-  <si>
     <t>Literaturrecherche, Bewertung von Untersuchungsideen, Zitation &amp; Referenzen</t>
   </si>
   <si>
-    <t>Forschungsfrage, Literaturrecherche &amp; Studienorganisation</t>
-  </si>
-  <si>
     <t>Code-Review</t>
   </si>
   <si>
-    <t>Auswertung von Studien - Teil 2: Ergebnisse und Datenvisualisierung</t>
-  </si>
-  <si>
-    <t>Auswertung von Studien - Teil 1: Datenvorbereitung, Stichprobenbeschreibung und Deskriptiv-Statistik</t>
+    <t>Puffer</t>
+  </si>
+  <si>
+    <t>Bis zum 31.10.: Abgabe Gruppenname &amp; Thema! ---- Feedback durch Caro, ist das Thema OK?</t>
+  </si>
+  <si>
+    <t>Ordnerstruktur, Literaturrecherche, Entwicklung Forschungsfrage, formr Einstieg</t>
+  </si>
+  <si>
+    <t>Auswertung von Studien - Teil 1: Datenvorbereitung</t>
+  </si>
+  <si>
+    <t>Auswertung von Studien - Teil 2: Deskriptiv-Statistik und Ergebnisse</t>
+  </si>
+  <si>
+    <t>Auswertung von Studien - Teil 3: Datenvisualisierung</t>
+  </si>
+  <si>
+    <t>p-hacking App</t>
+  </si>
+  <si>
+    <t>Bis zum 25.11.: Finalisierung Präregistrierung</t>
+  </si>
+  <si>
+    <t>Operationalisierung &amp; formr (Mittwoch &amp; Raumwechsel!)</t>
+  </si>
+  <si>
+    <t>Operationalisierung &amp; formr Implementierung &amp; Testdurchlauf</t>
+  </si>
+  <si>
+    <t>24.12.24 &amp; 31.12.24</t>
+  </si>
+  <si>
+    <t>entfallen wegen Weihnachtspause</t>
+  </si>
+  <si>
+    <t>15.10.24</t>
+  </si>
+  <si>
+    <t>22.10.24</t>
+  </si>
+  <si>
+    <t>29.10.24</t>
+  </si>
+  <si>
+    <t>06.11.24</t>
+  </si>
+  <si>
+    <t>12.11.24</t>
+  </si>
+  <si>
+    <t>19.11.24</t>
+  </si>
+  <si>
+    <t>26.11.24</t>
+  </si>
+  <si>
+    <t>03.12.24</t>
+  </si>
+  <si>
+    <t>10.12.24</t>
+  </si>
+  <si>
+    <t>17.12.24</t>
+  </si>
+  <si>
+    <t>07.01.25</t>
+  </si>
+  <si>
+    <t>14.01.25</t>
+  </si>
+  <si>
+    <t>21.01.25</t>
+  </si>
+  <si>
+    <t>28.01.25</t>
+  </si>
+  <si>
+    <t>04.02.25</t>
+  </si>
+  <si>
+    <t>Hypothesen, Studiendesign, erste Analysegedanken, formr ctd</t>
+  </si>
+  <si>
+    <t>optional: an wissenschaftlichem Bericht arbeiten</t>
+  </si>
+  <si>
+    <t>Gruppenfindung, OpenNotebook in GoogleDoc, Themenauswahl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Literaturrecherche &amp; Bewertung von Untersuchungsideen &amp; Zusammenarbeit in Gruppen &amp; Studienorganisation </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="d\.m\.yy"/>
-  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -222,7 +279,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -232,6 +289,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -248,9 +311,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -258,28 +320,33 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -295,10 +362,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -598,308 +661,323 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D16DFA94-C377-5646-8699-03C07B5DC979}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="24.625" style="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="86.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="52.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="65.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="35.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="70.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7">
-        <v>45392</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="G3" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>8</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="6" t="s">
+      <c r="D10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>9</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
         <v>10</v>
       </c>
-      <c r="G2" s="6"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="B13" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>11</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>12</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>13</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
-        <v>45399</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7">
-        <v>45406</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="6"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="10">
-        <v>45413</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="7">
-        <v>45420</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>5</v>
-      </c>
-      <c r="B7" s="7">
-        <v>45427</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="13">
-        <v>6</v>
-      </c>
-      <c r="B8" s="12">
-        <v>45434</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="10">
-        <v>45441</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="6"/>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <v>7</v>
-      </c>
-      <c r="B10" s="7">
-        <v>45448</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="6"/>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7">
-        <v>45455</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="6"/>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7">
-        <v>45462</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="6"/>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
-        <v>10</v>
-      </c>
-      <c r="B13" s="7">
-        <v>45469</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="6"/>
-      <c r="G13" s="6"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
-        <v>11</v>
-      </c>
-      <c r="B14" s="7">
-        <v>45476</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="6"/>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
-        <v>12</v>
-      </c>
-      <c r="B15" s="7">
-        <v>45483</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="6"/>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
-        <v>13</v>
-      </c>
-      <c r="B16" s="7">
-        <v>45490</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E16" s="6"/>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="1"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="4"/>
+      <c r="E17" s="5"/>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C21" s="1"/>
+      <c r="D21" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/WAF_Termine.xlsx
+++ b/WAF_Termine.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hochschulefresenius1-my.sharepoint.com/personal/caroline_zygar-hoffmann_charlotte-fresenius-uni_de/Documents/Lehre/WAF/WAF_Folien/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="377" documentId="13_ncr:1_{E1CA4565-1B9E-46AE-A3C7-26CD2293107D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26A8834A-2727-4622-B106-08AB628E727F}"/>
+  <xr:revisionPtr revIDLastSave="447" documentId="13_ncr:1_{E1CA4565-1B9E-46AE-A3C7-26CD2293107D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{431DC805-01F9-4185-900F-22F58F85CF94}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{2F7FBD6D-06A1-CD4E-B3C2-12F6DAD39F9F}"/>
+    <workbookView xWindow="390" yWindow="375" windowWidth="15330" windowHeight="10890" xr2:uid="{2F7FBD6D-06A1-CD4E-B3C2-12F6DAD39F9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
   <si>
     <t>Einheit</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Praxisteil Thema</t>
   </si>
   <si>
-    <t>entfällt wegen Zeitraum Wiederholungsprüfung</t>
-  </si>
-  <si>
     <t>Zusatzmaterial</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
     <t>Samplingplan &amp; Durchführung von Studien</t>
   </si>
   <si>
-    <t>Publikation von Studien mit Fokus auf Einleitung und Methode</t>
-  </si>
-  <si>
     <t>Publikation von Studien mit Fokus auf Ergebnisteil und Diskussion</t>
   </si>
   <si>
@@ -95,9 +89,6 @@
     <t>Review innerhalb von Gruppen</t>
   </si>
   <si>
-    <t>Template Präregistrierung</t>
-  </si>
-  <si>
     <t>Template/Anleitung formr</t>
   </si>
   <si>
@@ -122,110 +113,68 @@
     <t>Präregistrierung im Forschungsprozess &amp; Vorstellung Themenwahl</t>
   </si>
   <si>
-    <t>Literaturrecherche, Bewertung von Untersuchungsideen, Zitation &amp; Referenzen</t>
-  </si>
-  <si>
-    <t>Code-Review</t>
-  </si>
-  <si>
-    <t>Puffer</t>
-  </si>
-  <si>
-    <t>Bis zum 31.10.: Abgabe Gruppenname &amp; Thema! ---- Feedback durch Caro, ist das Thema OK?</t>
-  </si>
-  <si>
-    <t>Ordnerstruktur, Literaturrecherche, Entwicklung Forschungsfrage, formr Einstieg</t>
-  </si>
-  <si>
-    <t>Auswertung von Studien - Teil 1: Datenvorbereitung</t>
-  </si>
-  <si>
-    <t>Auswertung von Studien - Teil 2: Deskriptiv-Statistik und Ergebnisse</t>
-  </si>
-  <si>
-    <t>Auswertung von Studien - Teil 3: Datenvisualisierung</t>
-  </si>
-  <si>
-    <t>p-hacking App</t>
-  </si>
-  <si>
-    <t>Bis zum 25.11.: Finalisierung Präregistrierung</t>
-  </si>
-  <si>
-    <t>Operationalisierung &amp; formr (Mittwoch &amp; Raumwechsel!)</t>
-  </si>
-  <si>
     <t>Operationalisierung &amp; formr Implementierung &amp; Testdurchlauf</t>
   </si>
   <si>
-    <t>24.12.24 &amp; 31.12.24</t>
-  </si>
-  <si>
-    <t>entfallen wegen Weihnachtspause</t>
-  </si>
-  <si>
-    <t>15.10.24</t>
-  </si>
-  <si>
-    <t>22.10.24</t>
-  </si>
-  <si>
-    <t>29.10.24</t>
-  </si>
-  <si>
-    <t>06.11.24</t>
-  </si>
-  <si>
-    <t>12.11.24</t>
-  </si>
-  <si>
-    <t>19.11.24</t>
-  </si>
-  <si>
-    <t>26.11.24</t>
-  </si>
-  <si>
-    <t>03.12.24</t>
-  </si>
-  <si>
-    <t>10.12.24</t>
-  </si>
-  <si>
-    <t>17.12.24</t>
-  </si>
-  <si>
-    <t>07.01.25</t>
-  </si>
-  <si>
-    <t>14.01.25</t>
-  </si>
-  <si>
-    <t>21.01.25</t>
-  </si>
-  <si>
-    <t>28.01.25</t>
-  </si>
-  <si>
-    <t>04.02.25</t>
-  </si>
-  <si>
     <t>Hypothesen, Studiendesign, erste Analysegedanken, formr ctd</t>
   </si>
   <si>
-    <t>optional: an wissenschaftlichem Bericht arbeiten</t>
-  </si>
-  <si>
-    <t>Gruppenfindung, OpenNotebook in GoogleDoc, Themenauswahl</t>
-  </si>
-  <si>
     <t xml:space="preserve">Literaturrecherche &amp; Bewertung von Untersuchungsideen &amp; Zusammenarbeit in Gruppen &amp; Studienorganisation </t>
+  </si>
+  <si>
+    <t>Operationalisierung &amp; formr</t>
+  </si>
+  <si>
+    <t>Umgang mit KI</t>
+  </si>
+  <si>
+    <t>Literaturrecherche, Bewertung von Untersuchungsideen, Template Präregistrierung</t>
+  </si>
+  <si>
+    <t>Zitation &amp; Referenzen</t>
+  </si>
+  <si>
+    <t>Publikation von Studien mit Fokus auf Form, Einleitung und Methode</t>
+  </si>
+  <si>
+    <t>Weihnachtspause (Termin entfällt)</t>
+  </si>
+  <si>
+    <t>Feiertag (Termin entfällt)</t>
+  </si>
+  <si>
+    <t>Zeitraum Wiederholungsprüfung (Termin entfällt)</t>
+  </si>
+  <si>
+    <t>Bis zum 23.11..: Finalisierung Präregistrierung</t>
+  </si>
+  <si>
+    <t>Gruppenfindung in GoogleDoc, Themenauswahl</t>
+  </si>
+  <si>
+    <t>OpenNotebook, Ordnerstruktur, Literaturrecherche, Entwicklung Forschungsfrage, formr Einstieg</t>
+  </si>
+  <si>
+    <t>Bis zum 26.10.: Abgabe Gruppenname &amp; Thema! ---- Feedback durch Caro, ist das Thema OK?</t>
+  </si>
+  <si>
+    <t>Daten sammeln, Code-Review</t>
+  </si>
+  <si>
+    <t>Auswertung - Teil 1: Datenvorbereitung, Deskriptiv-Statistik und Ergebnisse</t>
+  </si>
+  <si>
+    <t>Auswertung - Teil 2: Datenvisualisierung</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="d\.m\.yy"/>
+  </numFmts>
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -271,15 +220,31 @@
       <scheme val="major"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri Light"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -289,12 +254,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -311,10 +270,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -326,27 +284,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -661,323 +615,338 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D16DFA94-C377-5646-8699-03C07B5DC979}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.625" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.625" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="86.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="65.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="35.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="70.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10">
+        <v>45944</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13">
+        <v>45951</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="13">
+        <v>45958</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13">
+        <v>45965</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10">
+        <v>45972</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="13">
+        <v>45979</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10">
+        <v>45986</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="11">
+        <v>45993</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10">
+        <v>46000</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>9</v>
+      </c>
+      <c r="B11" s="10">
+        <v>46007</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="D11" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="11">
+        <v>46014</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="11">
+        <v>46021</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="11">
+        <v>46028</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
         <v>10</v>
       </c>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+      <c r="B15" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>11</v>
+      </c>
+      <c r="B16" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>12</v>
+      </c>
+      <c r="B17" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>13</v>
+      </c>
+      <c r="B18" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="5"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="D18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="5"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
-        <v>6</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <v>7</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
-        <v>8</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="5"/>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
-        <v>9</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="5"/>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="5"/>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
-        <v>10</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="5"/>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
-        <v>11</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="5"/>
-      <c r="G14" s="5"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
-        <v>12</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="5"/>
-      <c r="G15" s="5"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
-        <v>13</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="G16" s="5"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
-        <v>14</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" s="5"/>
-      <c r="G17" s="5"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C21" s="1"/>
-      <c r="D21" s="3"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C20" s="1"/>
+      <c r="D20" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
